--- a/output/pdf_financials_xlsx/HAMR.xlsx
+++ b/output/pdf_financials_xlsx/HAMR.xlsx
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.267302</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.252634</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.688357</v>
       </c>
     </row>
     <row r="93">
@@ -3122,7 +3122,11 @@
           <t>Reserves 4</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -3467,7 +3471,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
         <v>2.267302</v>
       </c>

--- a/output/pdf_financials_xlsx/HAMR.xlsx
+++ b/output/pdf_financials_xlsx/HAMR.xlsx
@@ -580,10 +580,10 @@
         <v>0.373177</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.270943</v>
+        <v>1.575755</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.220115</v>
+        <v>0.802497</v>
       </c>
     </row>
     <row r="11">
@@ -596,10 +596,10 @@
         <v>-0.373177</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.270943</v>
+        <v>-1.575755</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.220115</v>
+        <v>-0.802497</v>
       </c>
     </row>
     <row r="12">
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.632232</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.035767</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.248302</v>
       </c>
     </row>
     <row r="35">
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.632232</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.035767</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.248302</v>
       </c>
     </row>
     <row r="37">
@@ -1218,13 +1218,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.308666</v>
+        <v>0.676434</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.049544</v>
+        <v>0.013777</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.26188</v>
+        <v>0.013578</v>
       </c>
     </row>
     <row r="49">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -2837,7 +2837,11 @@
           <t>Reclamation deposits 3</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -3312,7 +3316,11 @@
           <t>Reclamation deposits 4</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
         <v>0.030687</v>
       </c>
@@ -5010,7 +5018,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5019,10 +5027,10 @@
         </is>
       </c>
       <c r="F75" s="5" t="n">
-        <v>-1.575755</v>
+        <v>1.575755</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>-0.802497</v>
+        <v>0.802497</v>
       </c>
     </row>
     <row r="76">
